--- a/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260907-AGENT-B003/SEO_QA_B003.xlsx
+++ b/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260907-AGENT-B003/SEO_QA_B003.xlsx
@@ -14,11 +14,11 @@
     <sheet name="QA_Issues" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QA_Summary'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QA_Products'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QA_Summary'!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QA_Products'!$A$1:$T$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QA_Criteria'!$A$1:$J$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'QA_Images'!$A$1:$X$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA_Issues'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA_Issues'!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -618,76 +618,76 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Image_Audit rows visually checked via local B003 contact sheets and cross-checked with live gallery counts.</t>
+          <t>Image_Audit rows evaluated with evidence-driven rules over observation and alt fields; direct human visual confirmation remains a limitation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>batch_status</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>QA_PASS</t>
-        </is>
+          <t>image_rows_in_scope</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>All products QA_PASS; QA_PASS is not APPROVED.</t>
+          <t>Image_Audit rows included in this batch scope.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>batch_average_final_score</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>95</v>
+          <t>batch_status</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>QA_REVISE</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Equal average of product final scores.</t>
+          <t>Evidence-driven rerun status; QA_PASS requires complete assessed weight, score &gt;=85, and no CRITICAL/MAJOR.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>qa_pass_count</t>
+          <t>batch_average_final_score</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10</v>
+        <v>89.25</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Products meeting &gt;=85 with no CRITICAL/MAJOR.</t>
+          <t>Blank when any product has incomplete assessed weight.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>critical_count</t>
+          <t>qa_pass_count</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>No critical issue found.</t>
+          <t>Products meeting &gt;=85 with no CRITICAL/MAJOR.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>major_count</t>
+          <t>critical_count</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -695,61 +695,93 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Auto MAJOR identity/non-slip findings were downgraded/resolved after live and image QA; remaining deployment constraints are limitations.</t>
+          <t>Products with at least one CRITICAL issue.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>limitation_count</t>
+          <t>major_count</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state and direct demand evidence limitations; do not block content QA but must be acknowledged before approval/deploy.</t>
+          <t>Total MAJOR issues from evidence-driven field/image checks.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>generated_at</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
-        </is>
+          <t>limitation_count</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UTC timestamp.</t>
+          <t>Admin/export before-state, direct demand evidence, and visual-confirmation limitations.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>methodology_status</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>EVIDENCE_DRIVEN_RERUN_NO_FIXED_SCORE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>No fixed FULL/100/95 scoring is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>UTC timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>scope_note</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>QA covers B003 only; no workbook source edit, no approval, no Shopify deploy.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Operational boundary.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -760,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -780,8 +812,9 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -872,10 +905,15 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>limitation_count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>issue_refs</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>evidence_refs</t>
         </is>
@@ -898,19 +936,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -945,12 +983,15 @@
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0001;LIM-0002</t>
-        </is>
+      <c r="R2" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0001;LIM-0002;LIM-0003</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>B003-021; live HTTP=200; local contact sheet</t>
         </is>
@@ -973,23 +1014,23 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1020,12 +1061,15 @@
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0003;LIM-0004</t>
-        </is>
+      <c r="R3" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0004;LIM-0005;LIM-0006</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>B003-022; live HTTP=200; local contact sheet</t>
         </is>
@@ -1048,19 +1092,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -1095,12 +1139,15 @@
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0005;LIM-0006</t>
-        </is>
+      <c r="R4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0007;LIM-0008;LIM-0009</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>B003-023; live HTTP=200; local contact sheet</t>
         </is>
@@ -1123,19 +1170,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -1170,12 +1217,15 @@
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0007;LIM-0008</t>
-        </is>
+      <c r="R5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0010;LIM-0011;LIM-0012</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>B003-024; live HTTP=200; local contact sheet</t>
         </is>
@@ -1198,19 +1248,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -1245,12 +1295,15 @@
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0009;LIM-0010</t>
-        </is>
+      <c r="R6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0013;LIM-0014;LIM-0015</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>B003-025; live HTTP=200; local contact sheet</t>
         </is>
@@ -1273,19 +1326,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -1320,12 +1373,15 @@
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0011;LIM-0012</t>
-        </is>
+      <c r="R7" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0016;LIM-0017;LIM-0018</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>B003-026; live HTTP=200; local contact sheet</t>
         </is>
@@ -1348,19 +1404,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1395,12 +1451,15 @@
       <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0013;LIM-0014</t>
-        </is>
+      <c r="R8" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0019;LIM-0020;LIM-0021</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>B003-027; live HTTP=200; local contact sheet</t>
         </is>
@@ -1423,19 +1482,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1470,12 +1529,15 @@
       <c r="Q9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0015;LIM-0016</t>
-        </is>
+      <c r="R9" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0022;LIM-0023;LIM-0024</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>B003-028; live HTTP=200; local contact sheet</t>
         </is>
@@ -1498,19 +1560,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1545,12 +1607,15 @@
       <c r="Q10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0017;LIM-0018</t>
-        </is>
+      <c r="R10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025;LIM-0026;LIM-0027</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>B003-029; live HTTP=200; local contact sheet</t>
         </is>
@@ -1573,19 +1638,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>95</v>
+        <v>85.5</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>95</v>
+        <v>85.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>95</v>
+        <v>85.5</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>95</v>
+        <v>85.5</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1620,19 +1685,22 @@
       <c r="Q11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0019;LIM-0020</t>
-        </is>
+      <c r="R11" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
+          <t>LIM-0028;LIM-0029;LIM-0030</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t>B003-030; live HTTP=200; local contact sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:T11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -1667,7 +1735,7 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1752,7 +1820,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1792,7 +1860,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1832,7 +1900,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1872,7 +1940,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1898,21 +1966,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1922,7 +1990,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>LIM-0001;LIM-0002</t>
+          <t>LIM-0001;LIM-0002;LIM-0003</t>
         </is>
       </c>
     </row>
@@ -1956,7 +2024,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 35; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1996,7 +2064,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 35; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2036,7 +2104,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 134; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2076,7 +2144,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 64 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2094,29 +2162,29 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2124,7 +2192,11 @@
           <t>B003-021; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0001;LIM-0002;LIM-0003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2134,29 +2206,29 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2166,7 +2238,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>LIM-0001;LIM-0002</t>
+          <t>LIM-0001;LIM-0002;LIM-0003</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2272,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2240,7 +2312,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2280,7 +2352,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2320,7 +2392,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2346,21 +2418,21 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2370,7 +2442,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>LIM-0003;LIM-0004</t>
+          <t>LIM-0004;LIM-0005;LIM-0006</t>
         </is>
       </c>
     </row>
@@ -2390,21 +2462,21 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 32, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2430,21 +2502,21 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 32, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2484,7 +2556,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 120; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2524,7 +2596,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 62 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2542,29 +2614,29 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2572,7 +2644,11 @@
           <t>B003-022; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0004;LIM-0005;LIM-0006</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2582,29 +2658,29 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2614,7 +2690,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>LIM-0003;LIM-0004</t>
+          <t>LIM-0004;LIM-0005;LIM-0006</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2724,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2688,7 +2764,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2728,7 +2804,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2768,7 +2844,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2794,21 +2870,21 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2818,7 +2894,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005;LIM-0006</t>
+          <t>LIM-0007;LIM-0008;LIM-0009</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 37; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2892,7 +2968,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 37; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2932,7 +3008,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 131; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2972,7 +3048,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 62 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2990,29 +3066,29 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -3020,7 +3096,11 @@
           <t>B003-023; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0007;LIM-0008;LIM-0009</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3030,29 +3110,29 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -3062,7 +3142,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005;LIM-0006</t>
+          <t>LIM-0007;LIM-0008;LIM-0009</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3176,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3136,7 +3216,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3176,7 +3256,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3216,7 +3296,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3242,21 +3322,21 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3266,7 +3346,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>LIM-0007;LIM-0008</t>
+          <t>LIM-0010;LIM-0011;LIM-0012</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3380,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 41; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3340,7 +3420,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 41; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3380,7 +3460,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 135; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3420,7 +3500,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 64 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3438,29 +3518,29 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3468,7 +3548,11 @@
           <t>B003-024; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0010;LIM-0011;LIM-0012</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3478,29 +3562,29 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3510,7 +3594,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>LIM-0007;LIM-0008</t>
+          <t>LIM-0010;LIM-0011;LIM-0012</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3628,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3584,7 +3668,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -3624,7 +3708,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3664,7 +3748,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3690,21 +3774,21 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3714,7 +3798,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>LIM-0009;LIM-0010</t>
+          <t>LIM-0013;LIM-0014;LIM-0015</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3832,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 38; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3788,7 +3872,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 38; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3828,7 +3912,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 135; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3868,7 +3952,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 65 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3886,29 +3970,29 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3916,7 +4000,11 @@
           <t>B003-025; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0013;LIM-0014;LIM-0015</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3926,29 +4014,29 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3958,7 +4046,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>LIM-0009;LIM-0010</t>
+          <t>LIM-0013;LIM-0014;LIM-0015</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4080,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4032,7 +4120,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4072,7 +4160,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4112,7 +4200,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4138,21 +4226,21 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4162,7 +4250,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011;LIM-0012</t>
+          <t>LIM-0016;LIM-0017;LIM-0018</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4284,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 36; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4236,7 +4324,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 36; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4276,7 +4364,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 128; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4316,7 +4404,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 62 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -4334,29 +4422,29 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4364,7 +4452,11 @@
           <t>B003-026; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0016;LIM-0017;LIM-0018</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4374,29 +4466,29 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4406,7 +4498,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011;LIM-0012</t>
+          <t>LIM-0016;LIM-0017;LIM-0018</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4532,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4480,7 +4572,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4520,7 +4612,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4560,7 +4652,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -4586,21 +4678,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4610,7 +4702,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>LIM-0013;LIM-0014</t>
+          <t>LIM-0019;LIM-0020;LIM-0021</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4736,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 35; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4684,7 +4776,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 35; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4724,7 +4816,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 123; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4764,7 +4856,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 61 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4782,29 +4874,29 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4812,7 +4904,11 @@
           <t>B003-027; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0019;LIM-0020;LIM-0021</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4822,29 +4918,29 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4854,7 +4950,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>LIM-0013;LIM-0014</t>
+          <t>LIM-0019;LIM-0020;LIM-0021</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4984,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4928,7 +5024,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4968,7 +5064,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -5008,7 +5104,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -5034,21 +5130,21 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -5058,7 +5154,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>LIM-0015;LIM-0016</t>
+          <t>LIM-0022;LIM-0023;LIM-0024</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5188,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 36; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -5132,7 +5228,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 36; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -5172,7 +5268,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 131; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5212,7 +5308,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 64 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5230,29 +5326,29 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5260,7 +5356,11 @@
           <t>B003-028; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0022;LIM-0023;LIM-0024</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5270,29 +5370,29 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5302,7 +5402,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>LIM-0015;LIM-0016</t>
+          <t>LIM-0022;LIM-0023;LIM-0024</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5436,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5376,7 +5476,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Protected claims in proposed copy are supported by evidence/image observations.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5416,7 +5516,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5456,7 +5556,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5482,21 +5582,21 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5506,7 +5606,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017;LIM-0018</t>
+          <t>LIM-0025;LIM-0026;LIM-0027</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5640,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 39; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5580,7 +5680,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 39; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5620,7 +5720,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 131; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5660,7 +5760,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 65 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5678,29 +5778,29 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5708,7 +5808,11 @@
           <t>B003-029; live=https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025;LIM-0026;LIM-0027</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5718,29 +5822,29 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5750,7 +5854,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017;LIM-0018</t>
+          <t>LIM-0025;LIM-0026;LIM-0027</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5888,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5810,21 +5914,21 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>No protected claim conflict found, but claims are limited to workbook evidence.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5864,7 +5968,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5904,7 +6008,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5930,21 +6034,21 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5954,7 +6058,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>LIM-0019;LIM-0020</t>
+          <t>LIM-0028;LIM-0029;LIM-0030</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6092,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 36; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -6028,7 +6132,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 36; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -6068,7 +6172,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 133; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -6108,7 +6212,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 69 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -6126,29 +6230,29 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B003 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6156,7 +6260,11 @@
           <t>B003-030; live=https://chillgen.com/products/personalized-witch-area-rug-with-name-custom-halloween-rug-black</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0028;LIM-0029;LIM-0030</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6166,29 +6274,29 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B003 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -6198,7 +6306,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>LIM-0019;LIM-0020</t>
+          <t>LIM-0028;LIM-0029;LIM-0030</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6332,7 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="53" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
@@ -6399,17 +6507,17 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of tentacle checker vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -6429,12 +6537,12 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -6448,24 +6556,24 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_01.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -6503,17 +6611,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for tentacle checker vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -6533,12 +6641,12 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -6552,24 +6660,24 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_02.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -6607,17 +6715,17 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tentacle checker vortex Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -6637,12 +6745,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6656,24 +6764,24 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_03.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -6711,17 +6819,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tentacle checker vortex Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -6741,12 +6849,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6760,24 +6868,24 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_04.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -6815,17 +6923,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for tentacle checker vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -6845,12 +6953,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -6864,24 +6972,24 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_05.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -6919,17 +7027,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tentacle checker vortex Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -6949,12 +7057,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6968,24 +7076,24 @@
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_06.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -7023,17 +7131,17 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tentacle checker vortex Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -7053,12 +7161,12 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7072,24 +7180,24 @@
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_07.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -7127,17 +7235,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for tentacle checker vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -7157,12 +7265,12 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -7176,24 +7284,24 @@
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B003-021; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_08.jpg</t>
+          <t>B003-021; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -7231,17 +7339,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of black and white ghost vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -7261,12 +7369,12 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7280,24 +7388,24 @@
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_01.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -7335,17 +7443,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for black and white ghost vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -7365,12 +7473,12 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7384,24 +7492,24 @@
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_02.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -7439,17 +7547,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black and white ghost vortex Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -7469,12 +7577,12 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7488,24 +7596,24 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S12" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_03.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -7543,17 +7651,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black and white ghost vortex Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -7573,12 +7681,12 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7592,24 +7700,24 @@
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S13" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_04.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -7647,17 +7755,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for black and white ghost vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -7677,12 +7785,12 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7696,24 +7804,24 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_05.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -7751,17 +7859,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black and white ghost vortex Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -7781,12 +7889,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -7800,24 +7908,24 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S15" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_06.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -7855,17 +7963,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black and white ghost vortex Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -7885,12 +7993,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7904,24 +8012,24 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S16" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_07.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -7959,17 +8067,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for black and white ghost vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -7989,12 +8097,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8008,24 +8116,24 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S17" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>B003-022; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_08.jpg</t>
+          <t>B003-022; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -8063,17 +8171,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of pumpkin scarecrow vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -8093,12 +8201,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -8112,24 +8220,24 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_01.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8275,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for pumpkin scarecrow vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -8197,12 +8305,12 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8216,24 +8324,24 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S19" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_02.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -8271,17 +8379,17 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: pumpkin scarecrow vortex Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -8301,12 +8409,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8320,24 +8428,24 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S20" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_03.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -8375,17 +8483,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: pumpkin scarecrow vortex Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -8405,12 +8513,12 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -8424,24 +8532,24 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_04.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -8479,17 +8587,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for pumpkin scarecrow vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -8509,12 +8617,12 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8528,24 +8636,24 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S22" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_05.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -8583,17 +8691,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: pumpkin scarecrow vortex Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -8613,12 +8721,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8632,24 +8740,24 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_06.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -8687,17 +8795,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: pumpkin scarecrow vortex Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -8717,12 +8825,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8736,24 +8844,24 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S24" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_07.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -8791,17 +8899,17 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for pumpkin scarecrow vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -8821,12 +8929,12 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -8840,24 +8948,24 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S25" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>B003-023; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_08.jpg</t>
+          <t>B003-023; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -8895,17 +9003,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of rainbow spider web Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -8925,12 +9033,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8944,24 +9052,24 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S26" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_01.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -8999,17 +9107,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for rainbow spider web Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -9029,12 +9137,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -9048,24 +9156,24 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S27" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_02.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -9103,17 +9211,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: rainbow spider web Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -9133,12 +9241,12 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -9152,24 +9260,24 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S28" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_03.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -9207,17 +9315,17 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: rainbow spider web Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -9237,12 +9345,12 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -9256,24 +9364,24 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S29" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_04.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -9311,17 +9419,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for rainbow spider web rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -9341,12 +9449,12 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -9360,24 +9468,24 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S30" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_05.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -9415,17 +9523,17 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: rainbow spider web Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -9445,12 +9553,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -9464,24 +9572,24 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S31" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_06.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -9519,17 +9627,17 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: rainbow spider web Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -9549,12 +9657,12 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -9568,24 +9676,24 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S32" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_07.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -9623,17 +9731,17 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for rainbow spider web rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -9653,12 +9761,12 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -9672,24 +9780,24 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S33" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>B003-024; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_08.jpg</t>
+          <t>B003-024; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -9727,17 +9835,17 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of green ghost vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -9757,12 +9865,12 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -9776,24 +9884,24 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S34" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_01.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -9831,17 +9939,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for green ghost vortex Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -9861,12 +9969,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -9880,24 +9988,24 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S35" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_02.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -9935,17 +10043,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: green ghost vortex Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -9965,12 +10073,12 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -9984,24 +10092,24 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S36" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_03.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -10039,17 +10147,17 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: green ghost vortex Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -10069,12 +10177,12 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -10088,24 +10196,24 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S37" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_04.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -10143,17 +10251,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for green ghost vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -10173,12 +10281,12 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10192,24 +10300,24 @@
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S38" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_05.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -10247,17 +10355,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: green ghost vortex Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -10277,12 +10385,12 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -10296,24 +10404,24 @@
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S39" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_06.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -10351,17 +10459,17 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: green ghost vortex Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -10381,12 +10489,12 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -10400,24 +10508,24 @@
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S40" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_07.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -10455,17 +10563,17 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for green ghost vortex rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -10485,12 +10593,12 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10504,24 +10612,24 @@
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S41" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>B003-025; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_08.jpg</t>
+          <t>B003-025; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -10559,17 +10667,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of ghost staircase Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -10589,12 +10697,12 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -10608,24 +10716,24 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S42" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_01.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -10663,17 +10771,17 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for ghost staircase Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -10693,12 +10801,12 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -10712,24 +10820,24 @@
         </is>
       </c>
       <c r="R43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S43" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_02.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -10767,17 +10875,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost staircase Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -10797,12 +10905,12 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10816,24 +10924,24 @@
         </is>
       </c>
       <c r="R44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S44" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_03.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -10871,17 +10979,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost staircase Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -10901,12 +11009,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -10920,24 +11028,24 @@
         </is>
       </c>
       <c r="R45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S45" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_04.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -10975,17 +11083,17 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for ghost staircase rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -11005,12 +11113,12 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -11024,24 +11132,24 @@
         </is>
       </c>
       <c r="R46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S46" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_05.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -11079,17 +11187,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost staircase Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -11109,12 +11217,12 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -11128,24 +11236,24 @@
         </is>
       </c>
       <c r="R47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S47" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_06.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -11183,17 +11291,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost staircase Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -11213,12 +11321,12 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -11232,24 +11340,24 @@
         </is>
       </c>
       <c r="R48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S48" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_07.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -11287,17 +11395,17 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for ghost staircase rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -11317,12 +11425,12 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -11336,24 +11444,24 @@
         </is>
       </c>
       <c r="R49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S49" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>B003-026; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_08.jpg</t>
+          <t>B003-026; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11499,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of skeleton tunnel Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -11421,12 +11529,12 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -11440,24 +11548,24 @@
         </is>
       </c>
       <c r="R50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S50" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_01.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -11495,17 +11603,17 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for skeleton tunnel Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -11525,12 +11633,12 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -11544,24 +11652,24 @@
         </is>
       </c>
       <c r="R51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S51" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W51" s="2" t="inlineStr"/>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_02.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -11599,17 +11707,17 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: skeleton tunnel Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -11629,12 +11737,12 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -11648,24 +11756,24 @@
         </is>
       </c>
       <c r="R52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S52" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_03.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -11703,17 +11811,17 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: skeleton tunnel Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -11733,12 +11841,12 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -11752,24 +11860,24 @@
         </is>
       </c>
       <c r="R53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S53" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W53" s="2" t="inlineStr"/>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_04.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11915,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for skeleton tunnel rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -11837,12 +11945,12 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -11856,24 +11964,24 @@
         </is>
       </c>
       <c r="R54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S54" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_05.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -11911,17 +12019,17 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: skeleton tunnel Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -11941,12 +12049,12 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -11960,24 +12068,24 @@
         </is>
       </c>
       <c r="R55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S55" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W55" s="2" t="inlineStr"/>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_06.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -12015,17 +12123,17 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: skeleton tunnel Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -12045,12 +12153,12 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -12064,24 +12172,24 @@
         </is>
       </c>
       <c r="R56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S56" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W56" s="2" t="inlineStr"/>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_07.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -12119,17 +12227,17 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for skeleton tunnel rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -12149,12 +12257,12 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -12168,24 +12276,24 @@
         </is>
       </c>
       <c r="R57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S57" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W57" s="2" t="inlineStr"/>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>B003-027; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_08.jpg</t>
+          <t>B003-027; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12331,17 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of ghost stone well Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -12253,12 +12361,12 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -12272,24 +12380,24 @@
         </is>
       </c>
       <c r="R58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S58" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W58" s="2" t="inlineStr"/>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_01.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -12327,17 +12435,17 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for ghost stone well Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -12357,12 +12465,12 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -12376,24 +12484,24 @@
         </is>
       </c>
       <c r="R59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S59" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W59" s="2" t="inlineStr"/>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_02.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -12431,17 +12539,17 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost stone well Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -12461,12 +12569,12 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -12480,24 +12588,24 @@
         </is>
       </c>
       <c r="R60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S60" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W60" s="2" t="inlineStr"/>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_03.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -12535,17 +12643,17 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost stone well Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -12565,12 +12673,12 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -12584,24 +12692,24 @@
         </is>
       </c>
       <c r="R61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S61" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W61" s="2" t="inlineStr"/>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_04.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -12639,17 +12747,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for ghost stone well rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -12669,12 +12777,12 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -12688,24 +12796,24 @@
         </is>
       </c>
       <c r="R62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S62" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_05.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -12743,17 +12851,17 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost stone well Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -12773,12 +12881,12 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -12792,24 +12900,24 @@
         </is>
       </c>
       <c r="R63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S63" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_06.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -12847,17 +12955,17 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ghost stone well Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -12877,12 +12985,12 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -12896,24 +13004,24 @@
         </is>
       </c>
       <c r="R64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S64" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_07.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -12951,17 +13059,17 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for ghost stone well rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -12981,12 +13089,12 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -13000,24 +13108,24 @@
         </is>
       </c>
       <c r="R65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S65" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W65" s="2" t="inlineStr"/>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>B003-028; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_08.jpg</t>
+          <t>B003-028; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -13055,17 +13163,17 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: top view of jack-o-lantern vine Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -13085,12 +13193,12 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -13104,24 +13212,24 @@
         </is>
       </c>
       <c r="R66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S66" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_01.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -13159,17 +13267,17 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size chart for jack-o-lantern vine Halloween round rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -13189,12 +13297,12 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -13208,24 +13316,24 @@
         </is>
       </c>
       <c r="R67" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S67" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T67" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U67" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V67" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W67" s="2" t="inlineStr"/>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_02.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -13263,17 +13371,17 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: jack-o-lantern vine Halloween round rug shown underfoot</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -13293,12 +13401,12 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -13312,24 +13420,24 @@
         </is>
       </c>
       <c r="R68" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S68" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T68" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U68" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V68" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W68" s="2" t="inlineStr"/>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_03.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -13367,17 +13475,17 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: jack-o-lantern vine Halloween rug staged by fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -13397,12 +13505,12 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -13416,24 +13524,24 @@
         </is>
       </c>
       <c r="R69" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S69" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T69" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U69" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V69" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W69" s="2" t="inlineStr"/>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_04.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13579,17 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: non-slip backing detail for jack-o-lantern vine rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -13501,12 +13609,12 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -13520,24 +13628,24 @@
         </is>
       </c>
       <c r="R70" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S70" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T70" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U70" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V70" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W70" s="2" t="inlineStr"/>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_05.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -13575,17 +13683,17 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: jack-o-lantern vine Halloween rug in seasonal room mockup</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -13605,12 +13713,12 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -13624,24 +13732,24 @@
         </is>
       </c>
       <c r="R71" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S71" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T71" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U71" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V71" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W71" s="2" t="inlineStr"/>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_06.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -13679,17 +13787,17 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: jack-o-lantern vine Halloween round rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -13709,12 +13817,12 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -13728,24 +13836,24 @@
         </is>
       </c>
       <c r="R72" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S72" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T72" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U72" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V72" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W72" s="2" t="inlineStr"/>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_07.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -13783,17 +13891,17 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: design and backing detail for jack-o-lantern vine rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -13813,12 +13921,12 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -13832,24 +13940,24 @@
         </is>
       </c>
       <c r="R73" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S73" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T73" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V73" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W73" s="2" t="inlineStr"/>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>B003-029; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_08.jpg</t>
+          <t>B003-029; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13995,17 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: lifestyle view of black witch cat name rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -13917,12 +14025,12 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -13936,24 +14044,24 @@
         </is>
       </c>
       <c r="R74" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S74" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T74" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U74" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V74" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W74" s="2" t="inlineStr"/>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_01.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -13991,17 +14099,17 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: size information for black witch cat name rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -14021,12 +14129,12 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -14040,24 +14148,24 @@
         </is>
       </c>
       <c r="R75" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S75" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T75" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U75" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V75" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W75" s="2" t="inlineStr"/>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_02.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -14095,17 +14203,17 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black witch cat name rug staged near sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -14125,12 +14233,12 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -14144,24 +14252,24 @@
         </is>
       </c>
       <c r="R76" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S76" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T76" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U76" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V76" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W76" s="2" t="inlineStr"/>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_03.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -14199,17 +14307,17 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black witch cat name rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -14229,12 +14337,12 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -14248,24 +14356,24 @@
         </is>
       </c>
       <c r="R77" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S77" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T77" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U77" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V77" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W77" s="2" t="inlineStr"/>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_04.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14411,17 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: kid and pet friendly graphic for black witch cat name rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -14333,12 +14441,12 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -14352,24 +14460,24 @@
         </is>
       </c>
       <c r="R78" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S78" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T78" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U78" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V78" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W78" s="2" t="inlineStr"/>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_05.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -14407,17 +14515,17 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: cleaning options graphic for black witch cat name rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -14437,12 +14545,12 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -14456,24 +14564,24 @@
         </is>
       </c>
       <c r="R79" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S79" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T79" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U79" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V79" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W79" s="2" t="inlineStr"/>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_06.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -14511,17 +14619,17 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black witch cat name rug shown with family near fireplace</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -14541,12 +14649,12 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -14560,24 +14668,24 @@
         </is>
       </c>
       <c r="R80" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S80" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T80" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V80" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W80" s="2" t="inlineStr"/>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_07.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -14615,17 +14723,17 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:04:41.344371+00:00</t>
+          <t>2026-09-07T16:53:32.871706+00:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: black witch cat name rug under dining table</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -14645,12 +14753,12 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -14664,24 +14772,24 @@
         </is>
       </c>
       <c r="R81" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S81" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T81" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U81" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V81" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W81" s="2" t="inlineStr"/>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>B003-030; local B003 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_08.jpg</t>
+          <t>B003-030; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B003/personalized-witch-area-rug-with-name-custom-halloween-rug-black__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14966,7 +15074,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -14977,37 +15085,33 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04; B003-022</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-05; B003-021</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
@@ -15030,37 +15134,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
+          <t>admin_identity_and_admin_seo_fields</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>black white ghost vortex rug</t>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04; B003-022</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15176,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -15083,37 +15187,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
+          <t>keyword_demand_evidence</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+          <t>black white ghost vortex rug</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03; B003-023</t>
+          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15229,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
@@ -15136,37 +15240,33 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>pumpkin scarecrow Halloween rug</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-04; B003-022</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
@@ -15178,7 +15278,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -15214,7 +15314,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11; B003-024</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03; B003-023</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -15231,7 +15331,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
@@ -15247,7 +15347,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>spider web Halloween rug</t>
+          <t>pumpkin scarecrow Halloween rug</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -15284,7 +15384,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -15295,37 +15395,33 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01; B003-025</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-03; B003-023</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15433,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -15348,37 +15444,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
+          <t>admin_identity_and_admin_seo_fields</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>green ghost Halloween rug</t>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11; B003-024</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
         </is>
       </c>
     </row>
@@ -15390,7 +15486,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -15401,37 +15497,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
+          <t>keyword_demand_evidence</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+          <t>spider web Halloween rug</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08; B003-026</t>
+          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15539,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
@@ -15454,37 +15550,33 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>spiral ghost staircase Halloween rug</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-11; B003-024</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15588,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -15532,7 +15624,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09; B003-027</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01; B003-025</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -15549,7 +15641,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -15565,7 +15657,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>skeleton tunnel Halloween rug</t>
+          <t>green ghost Halloween rug</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15602,7 +15694,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -15613,37 +15705,33 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06; B003-028</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-01; B003-025</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15743,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -15666,37 +15754,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
+          <t>admin_identity_and_admin_seo_fields</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ghost stone well Halloween rug</t>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08; B003-026</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15796,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -15719,37 +15807,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
+          <t>keyword_demand_evidence</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+          <t>spiral ghost staircase Halloween rug</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02; B003-029</t>
+          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15849,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
@@ -15772,37 +15860,33 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>jack-o-lantern vine rug</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-08; B003-026</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15898,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-witch-area-rug-with-name-custom-halloween-rug-black</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -15850,7 +15934,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-witch-area-rug-with-name-custom-halloween-rug-black; B003-030</t>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09; B003-027</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -15867,7 +15951,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-witch-area-rug-with-name-custom-halloween-rug-black</t>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
@@ -15883,37 +15967,551 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>skeleton tunnel Halloween rug</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-09; B003-027</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06; B003-028</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ghost stone well Halloween rug</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-06; B003-028</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02; B003-029</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>jack-o-lantern vine rug</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-halloween-3d-optical-illusion-ghost-round-rug-design-02; B003-029</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-witch-area-rug-with-name-custom-halloween-rug-black</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B003 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-witch-area-rug-with-name-custom-halloween-rug-black; B003-030</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-witch-area-rug-with-name-custom-halloween-rug-black</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>personalized witch cat rug</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>https://www.walmart.com/c/kp/vortex-illusion-rug; https://www.etsy.com/market/illusion_stairs_rug; https://www.walmart.com/ip/Halloween-3D-Optical-Illusion-Round-Rug-Spooky-Staircase-Ghost-Pumpkin-Circular-Floor-Mat-Non-Slip-Absorbent-Decorative-Doormat-Halloween-Home-Party/20673415859; https://www.walmart.com/ip/3D-Haunted-Staircase-Round-Rug-Optical-Illusion-Halloween-Area-Mat/20840972139; https://chillgen.com/collections/halloween</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-witch-area-rug-with-name-custom-halloween-rug-black</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-witch-area-rug-with-name-custom-halloween-rug-black; B003-030</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:K31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -15935,6 +16533,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
